--- a/KatalonData/IWPTestData/DisplayCFData.xlsx
+++ b/KatalonData/IWPTestData/DisplayCFData.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5624" uniqueCount="530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6052" uniqueCount="637">
   <si>
     <t>Result</t>
   </si>
@@ -1641,6 +1641,327 @@
   </si>
   <si>
     <t>Thu Nov 13 21:10:33 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 20:18:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 20:19:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 20:21:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 20:22:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 20:24:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 20:26:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 20:27:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 20:29:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 20:31:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 20:32:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 20:33:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 20:35:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 20:36:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 20:38:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 20:40:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 20:41:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 20:43:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 20:44:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 20:45:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 20:47:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 20:49:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 20:50:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 20:52:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 20:53:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 20:55:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 20:56:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 20:57:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 20:59:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 21:01:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 21:02:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 21:04:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 21:06:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 21:07:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 21:09:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 21:10:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 21:12:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 21:13:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 21:15:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 21:17:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 21:18:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 21:20:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 21:21:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 21:22:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 21:24:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 21:26:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 21:28:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 21:29:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 21:31:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 21:33:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 19:33:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 19:38:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 19:39:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 19:41:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 19:43:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 19:44:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 19:46:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 19:47:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 19:49:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 19:50:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 19:51:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 19:52:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 19:54:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 19:56:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 19:57:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 19:59:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 20:01:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 20:02:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 20:03:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 20:05:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 20:06:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 20:08:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 20:09:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 20:11:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 20:13:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 20:14:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 20:15:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 20:16:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 20:18:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 20:20:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 20:21:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 20:23:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 20:24:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 20:26:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 20:27:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 20:28:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 20:30:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 20:31:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 20:33:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 20:35:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 20:36:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 20:38:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 20:39:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 20:40:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 20:42:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 20:44:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 20:45:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 20:47:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 20:49:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 20:50:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 20:56:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 20:59:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 21:03:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 21:05:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 21:06:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 21:07:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 21:08:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 26 21:10:02 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -5815,10 +6136,10 @@
     </row>
     <row ht="58" r="4" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>462</v>
+        <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>484</v>
+        <v>630</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>42</v>
@@ -5883,10 +6204,10 @@
     </row>
     <row ht="58" r="5" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>462</v>
+        <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>485</v>
+        <v>631</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>42</v>
@@ -5954,7 +6275,7 @@
         <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>486</v>
+        <v>632</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>42</v>
@@ -6019,10 +6340,10 @@
     </row>
     <row ht="58" r="7" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>462</v>
+        <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>487</v>
+        <v>633</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>42</v>
@@ -6087,10 +6408,10 @@
     </row>
     <row ht="58" r="8" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>462</v>
+        <v>63</v>
       </c>
       <c r="B8" t="s">
-        <v>488</v>
+        <v>634</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>42</v>
@@ -6158,7 +6479,7 @@
         <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>489</v>
+        <v>635</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>42</v>
@@ -6223,10 +6544,10 @@
     </row>
     <row ht="58" r="10" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>462</v>
+        <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>490</v>
+        <v>636</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>42</v>
@@ -18493,7 +18814,7 @@
         <v>63</v>
       </c>
       <c r="B2" t="s">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>28</v>
@@ -18560,7 +18881,7 @@
         <v>63</v>
       </c>
       <c r="B3" t="s">
-        <v>131</v>
+        <v>581</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>28</v>
@@ -18627,7 +18948,7 @@
         <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>132</v>
+        <v>582</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>28</v>
@@ -18694,7 +19015,7 @@
         <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>133</v>
+        <v>583</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>28</v>
@@ -18761,7 +19082,7 @@
         <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>134</v>
+        <v>584</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>28</v>
@@ -18828,7 +19149,7 @@
         <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>135</v>
+        <v>585</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>28</v>
@@ -18895,7 +19216,7 @@
         <v>63</v>
       </c>
       <c r="B8" t="s">
-        <v>136</v>
+        <v>586</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>28</v>
@@ -18962,7 +19283,7 @@
         <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>137</v>
+        <v>587</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>28</v>
@@ -19029,7 +19350,7 @@
         <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>138</v>
+        <v>588</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>28</v>
@@ -19096,7 +19417,7 @@
         <v>63</v>
       </c>
       <c r="B11" t="s">
-        <v>139</v>
+        <v>589</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>28</v>
@@ -19163,7 +19484,7 @@
         <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>140</v>
+        <v>590</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>28</v>
@@ -19230,7 +19551,7 @@
         <v>63</v>
       </c>
       <c r="B13" t="s">
-        <v>141</v>
+        <v>591</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>28</v>
@@ -19297,7 +19618,7 @@
         <v>63</v>
       </c>
       <c r="B14" t="s">
-        <v>142</v>
+        <v>592</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>28</v>
@@ -19364,7 +19685,7 @@
         <v>63</v>
       </c>
       <c r="B15" t="s">
-        <v>143</v>
+        <v>593</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>28</v>
@@ -19431,7 +19752,7 @@
         <v>63</v>
       </c>
       <c r="B16" t="s">
-        <v>144</v>
+        <v>594</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>28</v>
@@ -19498,7 +19819,7 @@
         <v>63</v>
       </c>
       <c r="B17" t="s">
-        <v>145</v>
+        <v>595</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>28</v>
@@ -19565,7 +19886,7 @@
         <v>63</v>
       </c>
       <c r="B18" t="s">
-        <v>146</v>
+        <v>596</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>28</v>
@@ -19632,7 +19953,7 @@
         <v>63</v>
       </c>
       <c r="B19" t="s">
-        <v>147</v>
+        <v>597</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>28</v>
@@ -19699,7 +20020,7 @@
         <v>63</v>
       </c>
       <c r="B20" t="s">
-        <v>148</v>
+        <v>598</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>28</v>
@@ -19766,7 +20087,7 @@
         <v>63</v>
       </c>
       <c r="B21" t="s">
-        <v>149</v>
+        <v>599</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>28</v>
@@ -19833,7 +20154,7 @@
         <v>63</v>
       </c>
       <c r="B22" t="s">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>28</v>
@@ -19900,7 +20221,7 @@
         <v>63</v>
       </c>
       <c r="B23" t="s">
-        <v>151</v>
+        <v>601</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>28</v>
@@ -19967,7 +20288,7 @@
         <v>63</v>
       </c>
       <c r="B24" t="s">
-        <v>152</v>
+        <v>602</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>28</v>
@@ -20034,7 +20355,7 @@
         <v>63</v>
       </c>
       <c r="B25" t="s">
-        <v>153</v>
+        <v>603</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>28</v>
@@ -20101,7 +20422,7 @@
         <v>63</v>
       </c>
       <c r="B26" t="s">
-        <v>154</v>
+        <v>604</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>28</v>
@@ -20168,7 +20489,7 @@
         <v>63</v>
       </c>
       <c r="B27" t="s">
-        <v>155</v>
+        <v>605</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>28</v>
@@ -20235,7 +20556,7 @@
         <v>63</v>
       </c>
       <c r="B28" t="s">
-        <v>156</v>
+        <v>606</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>28</v>
@@ -20302,7 +20623,7 @@
         <v>63</v>
       </c>
       <c r="B29" t="s">
-        <v>157</v>
+        <v>607</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>28</v>
@@ -20369,7 +20690,7 @@
         <v>63</v>
       </c>
       <c r="B30" t="s">
-        <v>158</v>
+        <v>608</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>28</v>
@@ -20436,7 +20757,7 @@
         <v>63</v>
       </c>
       <c r="B31" t="s">
-        <v>159</v>
+        <v>609</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>28</v>
@@ -20503,7 +20824,7 @@
         <v>63</v>
       </c>
       <c r="B32" t="s">
-        <v>160</v>
+        <v>610</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>28</v>
@@ -20570,7 +20891,7 @@
         <v>63</v>
       </c>
       <c r="B33" t="s">
-        <v>161</v>
+        <v>611</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>28</v>
@@ -20637,7 +20958,7 @@
         <v>63</v>
       </c>
       <c r="B34" t="s">
-        <v>162</v>
+        <v>612</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>28</v>
@@ -20704,7 +21025,7 @@
         <v>63</v>
       </c>
       <c r="B35" t="s">
-        <v>163</v>
+        <v>613</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>28</v>
@@ -20771,7 +21092,7 @@
         <v>63</v>
       </c>
       <c r="B36" t="s">
-        <v>164</v>
+        <v>614</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>28</v>
@@ -20838,7 +21159,7 @@
         <v>63</v>
       </c>
       <c r="B37" t="s">
-        <v>165</v>
+        <v>615</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>28</v>
@@ -20905,7 +21226,7 @@
         <v>63</v>
       </c>
       <c r="B38" t="s">
-        <v>166</v>
+        <v>616</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>28</v>
@@ -20972,7 +21293,7 @@
         <v>63</v>
       </c>
       <c r="B39" t="s">
-        <v>167</v>
+        <v>617</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>28</v>
@@ -21039,7 +21360,7 @@
         <v>63</v>
       </c>
       <c r="B40" t="s">
-        <v>168</v>
+        <v>618</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>28</v>
@@ -21106,7 +21427,7 @@
         <v>63</v>
       </c>
       <c r="B41" t="s">
-        <v>169</v>
+        <v>619</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>28</v>
@@ -21173,7 +21494,7 @@
         <v>63</v>
       </c>
       <c r="B42" t="s">
-        <v>170</v>
+        <v>620</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>28</v>
@@ -21240,7 +21561,7 @@
         <v>63</v>
       </c>
       <c r="B43" t="s">
-        <v>171</v>
+        <v>621</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>28</v>
@@ -21307,7 +21628,7 @@
         <v>63</v>
       </c>
       <c r="B44" t="s">
-        <v>172</v>
+        <v>622</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>28</v>
@@ -21374,7 +21695,7 @@
         <v>63</v>
       </c>
       <c r="B45" t="s">
-        <v>173</v>
+        <v>623</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>28</v>
@@ -21441,7 +21762,7 @@
         <v>63</v>
       </c>
       <c r="B46" t="s">
-        <v>174</v>
+        <v>624</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>28</v>
@@ -21508,7 +21829,7 @@
         <v>63</v>
       </c>
       <c r="B47" t="s">
-        <v>175</v>
+        <v>625</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>28</v>
@@ -21575,7 +21896,7 @@
         <v>63</v>
       </c>
       <c r="B48" t="s">
-        <v>176</v>
+        <v>626</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>28</v>
@@ -21642,7 +21963,7 @@
         <v>63</v>
       </c>
       <c r="B49" t="s">
-        <v>177</v>
+        <v>627</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>28</v>
@@ -21709,7 +22030,7 @@
         <v>63</v>
       </c>
       <c r="B50" t="s">
-        <v>178</v>
+        <v>628</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>28</v>

--- a/KatalonData/IWPTestData/DisplayCFData.xlsx
+++ b/KatalonData/IWPTestData/DisplayCFData.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6052" uniqueCount="637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6060" uniqueCount="639">
   <si>
     <t>Result</t>
   </si>
@@ -1962,6 +1962,12 @@
   </si>
   <si>
     <t>Mon Jan 26 21:10:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 22:58:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 23:01:22 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -2463,7 +2469,7 @@
         <v>63</v>
       </c>
       <c r="B2" t="s">
-        <v>296</v>
+        <v>638</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>28</v>

--- a/KatalonData/IWPTestData/DisplayCFData.xlsx
+++ b/KatalonData/IWPTestData/DisplayCFData.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6060" uniqueCount="639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7048" uniqueCount="886">
   <si>
     <t>Result</t>
   </si>
@@ -1968,6 +1968,747 @@
   </si>
   <si>
     <t>Wed Feb 18 23:01:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 13:59:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:01:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:03:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:04:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:05:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:06:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:07:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:08:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:10:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:11:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:12:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:13:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:14:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:15:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:16:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:17:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:19:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:20:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:21:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:22:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:23:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:24:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:25:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:26:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:27:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:29:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:30:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:31:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:32:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:33:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:34:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:35:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:36:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:37:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:39:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:40:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:41:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:42:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:43:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:44:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:45:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:46:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:47:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:49:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:50:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:51:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:52:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:53:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:54:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:55:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:56:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:57:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 14:58:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:00:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:01:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:02:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:03:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:04:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:05:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:06:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:07:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:08:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:10:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:11:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:12:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:13:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:14:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:15:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:16:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:17:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:18:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:20:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:21:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:22:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:23:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:24:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:25:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:26:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:27:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:28:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:29:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:30:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:31:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:33:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:35:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:40:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:41:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:42:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:43:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:45:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:46:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:47:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:48:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:49:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:50:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:51:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:52:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:53:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:55:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:56:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:57:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:58:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 15:59:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:01:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:03:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:04:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:06:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:07:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:08:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:10:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:11:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:13:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:14:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:16:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:17:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:19:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:20:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:21:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:23:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:24:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:26:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:28:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:29:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:31:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:32:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:33:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:34:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:36:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:38:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:39:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:41:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:43:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:44:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:45:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:46:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:48:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:49:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:51:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:52:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:54:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:55:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:56:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:58:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 16:59:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:01:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:03:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:04:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:06:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:07:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:09:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:10:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:12:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:13:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:14:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:16:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:17:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:19:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:20:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:21:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:23:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:24:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:25:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:26:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:28:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:29:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:30:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:31:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:33:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:34:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:35:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:36:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:38:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:39:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:40:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:41:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:43:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:44:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:45:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:46:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:47:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:48:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:49:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:50:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:51:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:52:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:54:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:55:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:56:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:57:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:58:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:59:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:00:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:02:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:03:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:04:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:05:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:06:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:07:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:08:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:09:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:10:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:12:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:13:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:14:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:15:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:16:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:17:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:18:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:19:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:20:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:21:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:22:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:24:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:24:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:26:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:27:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:28:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:29:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:30:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:31:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:32:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:33:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:34:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:35:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:36:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:38:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:39:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:40:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:41:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:42:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:43:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:44:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:45:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:46:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:48:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:49:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:50:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:51:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:52:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:53:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:54:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:55:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:56:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:57:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 18:58:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 19:44:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 19:46:01 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -2469,7 +3210,7 @@
         <v>63</v>
       </c>
       <c r="B2" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>28</v>
@@ -6213,7 +6954,7 @@
         <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>631</v>
+        <v>824</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>42</v>
@@ -6281,7 +7022,7 @@
         <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>632</v>
+        <v>825</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>42</v>
@@ -6349,7 +7090,7 @@
         <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>633</v>
+        <v>826</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>42</v>
@@ -6417,7 +7158,7 @@
         <v>63</v>
       </c>
       <c r="B8" t="s">
-        <v>634</v>
+        <v>827</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>42</v>
@@ -6485,7 +7226,7 @@
         <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>635</v>
+        <v>828</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>42</v>
@@ -6553,7 +7294,7 @@
         <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>636</v>
+        <v>829</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>42</v>
@@ -6864,10 +7605,10 @@
     </row>
     <row ht="58" r="2" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>462</v>
+        <v>63</v>
       </c>
       <c r="B2" t="s">
-        <v>491</v>
+        <v>830</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>42</v>
@@ -6935,7 +7676,7 @@
         <v>63</v>
       </c>
       <c r="B3" t="s">
-        <v>492</v>
+        <v>831</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>42</v>
@@ -7000,10 +7741,10 @@
     </row>
     <row ht="58" r="4" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>462</v>
+        <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>493</v>
+        <v>832</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>42</v>
@@ -7071,7 +7812,7 @@
         <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>494</v>
+        <v>833</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>42</v>
@@ -7139,7 +7880,7 @@
         <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>495</v>
+        <v>834</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>42</v>
@@ -7207,7 +7948,7 @@
         <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>496</v>
+        <v>835</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>42</v>
@@ -7275,7 +8016,7 @@
         <v>63</v>
       </c>
       <c r="B8" t="s">
-        <v>497</v>
+        <v>836</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>42</v>
@@ -7340,10 +8081,10 @@
     </row>
     <row ht="58" r="9" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>462</v>
+        <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>498</v>
+        <v>837</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>42</v>
@@ -7408,10 +8149,10 @@
     </row>
     <row ht="58" r="10" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>462</v>
+        <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>499</v>
+        <v>838</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>42</v>
@@ -7724,7 +8465,7 @@
         <v>63</v>
       </c>
       <c r="B2" t="s">
-        <v>500</v>
+        <v>839</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>42</v>
@@ -7792,7 +8533,7 @@
         <v>63</v>
       </c>
       <c r="B3" t="s">
-        <v>501</v>
+        <v>840</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>42</v>
@@ -7860,7 +8601,7 @@
         <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>502</v>
+        <v>841</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>42</v>
@@ -7928,7 +8669,7 @@
         <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>503</v>
+        <v>842</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>42</v>
@@ -7996,7 +8737,7 @@
         <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>504</v>
+        <v>843</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>42</v>
@@ -8064,7 +8805,7 @@
         <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>505</v>
+        <v>844</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>42</v>
@@ -8132,7 +8873,7 @@
         <v>63</v>
       </c>
       <c r="B8" t="s">
-        <v>506</v>
+        <v>845</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>42</v>
@@ -8200,7 +8941,7 @@
         <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>507</v>
+        <v>846</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>42</v>
@@ -8268,7 +9009,7 @@
         <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>508</v>
+        <v>847</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>42</v>
@@ -8586,7 +9327,7 @@
         <v>63</v>
       </c>
       <c r="B2" t="s">
-        <v>427</v>
+        <v>848</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>42</v>
@@ -8654,7 +9395,7 @@
         <v>63</v>
       </c>
       <c r="B3" t="s">
-        <v>428</v>
+        <v>849</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>42</v>
@@ -8722,7 +9463,7 @@
         <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>429</v>
+        <v>850</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>42</v>
@@ -8790,7 +9531,7 @@
         <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>430</v>
+        <v>851</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>42</v>
@@ -8858,7 +9599,7 @@
         <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>431</v>
+        <v>852</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>42</v>
@@ -8926,7 +9667,7 @@
         <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>432</v>
+        <v>853</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>42</v>
@@ -8994,7 +9735,7 @@
         <v>63</v>
       </c>
       <c r="B8" t="s">
-        <v>433</v>
+        <v>854</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>42</v>
@@ -9062,7 +9803,7 @@
         <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>434</v>
+        <v>855</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>42</v>
@@ -9130,7 +9871,7 @@
         <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>435</v>
+        <v>856</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>42</v>
@@ -9447,7 +10188,7 @@
         <v>63</v>
       </c>
       <c r="B2" t="s">
-        <v>436</v>
+        <v>857</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>42</v>
@@ -9515,7 +10256,7 @@
         <v>63</v>
       </c>
       <c r="B3" t="s">
-        <v>437</v>
+        <v>858</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>42</v>
@@ -9583,7 +10324,7 @@
         <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>438</v>
+        <v>859</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>42</v>
@@ -9651,7 +10392,7 @@
         <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>439</v>
+        <v>860</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>42</v>
@@ -9719,7 +10460,7 @@
         <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>440</v>
+        <v>861</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>42</v>
@@ -9787,7 +10528,7 @@
         <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>441</v>
+        <v>862</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>42</v>
@@ -9855,7 +10596,7 @@
         <v>63</v>
       </c>
       <c r="B8" t="s">
-        <v>442</v>
+        <v>863</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>42</v>
@@ -9923,7 +10664,7 @@
         <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>443</v>
+        <v>864</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>42</v>
@@ -9991,7 +10732,7 @@
         <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>444</v>
+        <v>865</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>42</v>
@@ -10304,7 +11045,7 @@
         <v>63</v>
       </c>
       <c r="B2" t="s">
-        <v>445</v>
+        <v>866</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>42</v>
@@ -10372,7 +11113,7 @@
         <v>63</v>
       </c>
       <c r="B3" t="s">
-        <v>446</v>
+        <v>867</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>42</v>
@@ -10440,7 +11181,7 @@
         <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>447</v>
+        <v>868</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>42</v>
@@ -10508,7 +11249,7 @@
         <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>448</v>
+        <v>869</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>42</v>
@@ -10576,7 +11317,7 @@
         <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>449</v>
+        <v>870</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>42</v>
@@ -10644,7 +11385,7 @@
         <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>450</v>
+        <v>871</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>42</v>
@@ -10712,7 +11453,7 @@
         <v>63</v>
       </c>
       <c r="B8" t="s">
-        <v>451</v>
+        <v>872</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>42</v>
@@ -10780,7 +11521,7 @@
         <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>452</v>
+        <v>873</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>42</v>
@@ -10848,7 +11589,7 @@
         <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>453</v>
+        <v>874</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>42</v>
@@ -11161,7 +11902,7 @@
         <v>63</v>
       </c>
       <c r="B2" t="s">
-        <v>464</v>
+        <v>875</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>42</v>
@@ -11229,7 +11970,7 @@
         <v>63</v>
       </c>
       <c r="B3" t="s">
-        <v>465</v>
+        <v>876</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>42</v>
@@ -11297,7 +12038,7 @@
         <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>466</v>
+        <v>877</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>42</v>
@@ -11365,7 +12106,7 @@
         <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>467</v>
+        <v>878</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>42</v>
@@ -11433,7 +12174,7 @@
         <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>468</v>
+        <v>879</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>42</v>
@@ -11501,7 +12242,7 @@
         <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>469</v>
+        <v>880</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>42</v>
@@ -11569,7 +12310,7 @@
         <v>63</v>
       </c>
       <c r="B8" t="s">
-        <v>470</v>
+        <v>881</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>42</v>
@@ -11637,7 +12378,7 @@
         <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>471</v>
+        <v>882</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>42</v>
@@ -11705,7 +12446,7 @@
         <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>472</v>
+        <v>883</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>42</v>
@@ -12015,7 +12756,7 @@
         <v>63</v>
       </c>
       <c r="B2" t="s">
-        <v>347</v>
+        <v>640</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>28</v>
@@ -12082,7 +12823,7 @@
         <v>63</v>
       </c>
       <c r="B3" t="s">
-        <v>348</v>
+        <v>641</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>28</v>
@@ -12149,7 +12890,7 @@
         <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>349</v>
+        <v>642</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>28</v>
@@ -12216,7 +12957,7 @@
         <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>350</v>
+        <v>643</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>28</v>
@@ -12283,7 +13024,7 @@
         <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>351</v>
+        <v>644</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>28</v>
@@ -12350,7 +13091,7 @@
         <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>352</v>
+        <v>645</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>28</v>
@@ -12417,7 +13158,7 @@
         <v>63</v>
       </c>
       <c r="B8" t="s">
-        <v>353</v>
+        <v>646</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>28</v>
@@ -12484,7 +13225,7 @@
         <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>354</v>
+        <v>647</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>28</v>
@@ -12551,7 +13292,7 @@
         <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>355</v>
+        <v>648</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>28</v>
@@ -12618,7 +13359,7 @@
         <v>63</v>
       </c>
       <c r="B11" t="s">
-        <v>356</v>
+        <v>649</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>28</v>
@@ -12685,7 +13426,7 @@
         <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>357</v>
+        <v>650</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>28</v>
@@ -12752,7 +13493,7 @@
         <v>63</v>
       </c>
       <c r="B13" t="s">
-        <v>358</v>
+        <v>651</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>28</v>
@@ -12819,7 +13560,7 @@
         <v>63</v>
       </c>
       <c r="B14" t="s">
-        <v>359</v>
+        <v>652</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>28</v>
@@ -12886,7 +13627,7 @@
         <v>63</v>
       </c>
       <c r="B15" t="s">
-        <v>360</v>
+        <v>653</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>28</v>
@@ -12953,7 +13694,7 @@
         <v>63</v>
       </c>
       <c r="B16" t="s">
-        <v>361</v>
+        <v>654</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>28</v>
@@ -13020,7 +13761,7 @@
         <v>63</v>
       </c>
       <c r="B17" t="s">
-        <v>362</v>
+        <v>655</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>28</v>
@@ -13087,7 +13828,7 @@
         <v>63</v>
       </c>
       <c r="B18" t="s">
-        <v>363</v>
+        <v>656</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>28</v>
@@ -13154,7 +13895,7 @@
         <v>63</v>
       </c>
       <c r="B19" t="s">
-        <v>364</v>
+        <v>657</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>28</v>
@@ -13221,7 +13962,7 @@
         <v>63</v>
       </c>
       <c r="B20" t="s">
-        <v>365</v>
+        <v>658</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>28</v>
@@ -13288,7 +14029,7 @@
         <v>63</v>
       </c>
       <c r="B21" t="s">
-        <v>366</v>
+        <v>659</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>28</v>
@@ -13355,7 +14096,7 @@
         <v>63</v>
       </c>
       <c r="B22" t="s">
-        <v>367</v>
+        <v>660</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>28</v>
@@ -13422,7 +14163,7 @@
         <v>63</v>
       </c>
       <c r="B23" t="s">
-        <v>368</v>
+        <v>661</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>28</v>
@@ -13489,7 +14230,7 @@
         <v>63</v>
       </c>
       <c r="B24" t="s">
-        <v>369</v>
+        <v>662</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>28</v>
@@ -13556,7 +14297,7 @@
         <v>63</v>
       </c>
       <c r="B25" t="s">
-        <v>370</v>
+        <v>663</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>28</v>
@@ -13623,7 +14364,7 @@
         <v>63</v>
       </c>
       <c r="B26" t="s">
-        <v>371</v>
+        <v>664</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>28</v>
@@ -13690,7 +14431,7 @@
         <v>63</v>
       </c>
       <c r="B27" t="s">
-        <v>372</v>
+        <v>665</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>28</v>
@@ -13757,7 +14498,7 @@
         <v>63</v>
       </c>
       <c r="B28" t="s">
-        <v>373</v>
+        <v>666</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>28</v>
@@ -13824,7 +14565,7 @@
         <v>63</v>
       </c>
       <c r="B29" t="s">
-        <v>374</v>
+        <v>667</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>28</v>
@@ -13891,7 +14632,7 @@
         <v>63</v>
       </c>
       <c r="B30" t="s">
-        <v>375</v>
+        <v>668</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>28</v>
@@ -13958,7 +14699,7 @@
         <v>63</v>
       </c>
       <c r="B31" t="s">
-        <v>376</v>
+        <v>669</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>28</v>
@@ -14025,7 +14766,7 @@
         <v>63</v>
       </c>
       <c r="B32" t="s">
-        <v>377</v>
+        <v>670</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>28</v>
@@ -14092,7 +14833,7 @@
         <v>63</v>
       </c>
       <c r="B33" t="s">
-        <v>378</v>
+        <v>671</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>28</v>
@@ -14159,7 +14900,7 @@
         <v>63</v>
       </c>
       <c r="B34" t="s">
-        <v>379</v>
+        <v>672</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>28</v>
@@ -14226,7 +14967,7 @@
         <v>63</v>
       </c>
       <c r="B35" t="s">
-        <v>380</v>
+        <v>673</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>28</v>
@@ -14293,7 +15034,7 @@
         <v>63</v>
       </c>
       <c r="B36" t="s">
-        <v>381</v>
+        <v>674</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>28</v>
@@ -14360,7 +15101,7 @@
         <v>63</v>
       </c>
       <c r="B37" t="s">
-        <v>382</v>
+        <v>675</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>28</v>
@@ -14427,7 +15168,7 @@
         <v>63</v>
       </c>
       <c r="B38" t="s">
-        <v>383</v>
+        <v>676</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>28</v>
@@ -14494,7 +15235,7 @@
         <v>63</v>
       </c>
       <c r="B39" t="s">
-        <v>384</v>
+        <v>677</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>28</v>
@@ -14561,7 +15302,7 @@
         <v>63</v>
       </c>
       <c r="B40" t="s">
-        <v>385</v>
+        <v>678</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>28</v>
@@ -14628,7 +15369,7 @@
         <v>63</v>
       </c>
       <c r="B41" t="s">
-        <v>386</v>
+        <v>679</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>28</v>
@@ -14695,7 +15436,7 @@
         <v>63</v>
       </c>
       <c r="B42" t="s">
-        <v>387</v>
+        <v>680</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>28</v>
@@ -14762,7 +15503,7 @@
         <v>63</v>
       </c>
       <c r="B43" t="s">
-        <v>388</v>
+        <v>681</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>28</v>
@@ -14829,7 +15570,7 @@
         <v>63</v>
       </c>
       <c r="B44" t="s">
-        <v>389</v>
+        <v>682</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>28</v>
@@ -14896,7 +15637,7 @@
         <v>63</v>
       </c>
       <c r="B45" t="s">
-        <v>390</v>
+        <v>683</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>28</v>
@@ -14963,7 +15704,7 @@
         <v>63</v>
       </c>
       <c r="B46" t="s">
-        <v>391</v>
+        <v>684</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>28</v>
@@ -15030,7 +15771,7 @@
         <v>63</v>
       </c>
       <c r="B47" t="s">
-        <v>392</v>
+        <v>685</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>28</v>
@@ -15097,7 +15838,7 @@
         <v>63</v>
       </c>
       <c r="B48" t="s">
-        <v>393</v>
+        <v>686</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>28</v>
@@ -15164,7 +15905,7 @@
         <v>63</v>
       </c>
       <c r="B49" t="s">
-        <v>394</v>
+        <v>687</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>28</v>
@@ -15231,7 +15972,7 @@
         <v>63</v>
       </c>
       <c r="B50" t="s">
-        <v>395</v>
+        <v>688</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>28</v>
@@ -15421,7 +16162,7 @@
         <v>63</v>
       </c>
       <c r="B2" t="s">
-        <v>261</v>
+        <v>689</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>28</v>
@@ -15488,7 +16229,7 @@
         <v>63</v>
       </c>
       <c r="B3" t="s">
-        <v>262</v>
+        <v>690</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>28</v>
@@ -15555,7 +16296,7 @@
         <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>263</v>
+        <v>691</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>28</v>
@@ -15622,7 +16363,7 @@
         <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>264</v>
+        <v>692</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>28</v>
@@ -15689,7 +16430,7 @@
         <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>265</v>
+        <v>693</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>28</v>
@@ -15756,7 +16497,7 @@
         <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>266</v>
+        <v>694</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>28</v>
@@ -15823,7 +16564,7 @@
         <v>63</v>
       </c>
       <c r="B8" t="s">
-        <v>267</v>
+        <v>695</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>28</v>
@@ -15890,7 +16631,7 @@
         <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>268</v>
+        <v>696</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>28</v>
@@ -15957,7 +16698,7 @@
         <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>269</v>
+        <v>697</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>28</v>
@@ -16024,7 +16765,7 @@
         <v>63</v>
       </c>
       <c r="B11" t="s">
-        <v>270</v>
+        <v>698</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>28</v>
@@ -16091,7 +16832,7 @@
         <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>396</v>
+        <v>699</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>28</v>
@@ -16158,7 +16899,7 @@
         <v>63</v>
       </c>
       <c r="B13" t="s">
-        <v>397</v>
+        <v>700</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>28</v>
@@ -16225,7 +16966,7 @@
         <v>63</v>
       </c>
       <c r="B14" t="s">
-        <v>271</v>
+        <v>701</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>28</v>
@@ -16292,7 +17033,7 @@
         <v>63</v>
       </c>
       <c r="B15" t="s">
-        <v>272</v>
+        <v>702</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>28</v>
@@ -16359,7 +17100,7 @@
         <v>63</v>
       </c>
       <c r="B16" t="s">
-        <v>273</v>
+        <v>703</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>28</v>
@@ -16426,7 +17167,7 @@
         <v>63</v>
       </c>
       <c r="B17" t="s">
-        <v>274</v>
+        <v>704</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>28</v>
@@ -16493,7 +17234,7 @@
         <v>63</v>
       </c>
       <c r="B18" t="s">
-        <v>275</v>
+        <v>705</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>28</v>
@@ -16560,7 +17301,7 @@
         <v>63</v>
       </c>
       <c r="B19" t="s">
-        <v>276</v>
+        <v>706</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>28</v>
@@ -16627,7 +17368,7 @@
         <v>63</v>
       </c>
       <c r="B20" t="s">
-        <v>277</v>
+        <v>707</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>28</v>
@@ -16694,7 +17435,7 @@
         <v>63</v>
       </c>
       <c r="B21" t="s">
-        <v>278</v>
+        <v>708</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>28</v>
@@ -16761,7 +17502,7 @@
         <v>63</v>
       </c>
       <c r="B22" t="s">
-        <v>279</v>
+        <v>709</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>28</v>
@@ -16828,7 +17569,7 @@
         <v>63</v>
       </c>
       <c r="B23" t="s">
-        <v>280</v>
+        <v>710</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>28</v>
@@ -16895,7 +17636,7 @@
         <v>63</v>
       </c>
       <c r="B24" t="s">
-        <v>281</v>
+        <v>711</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>28</v>
@@ -16962,7 +17703,7 @@
         <v>63</v>
       </c>
       <c r="B25" t="s">
-        <v>282</v>
+        <v>712</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>28</v>
@@ -17029,7 +17770,7 @@
         <v>63</v>
       </c>
       <c r="B26" t="s">
-        <v>283</v>
+        <v>713</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>28</v>
@@ -17096,7 +17837,7 @@
         <v>63</v>
       </c>
       <c r="B27" t="s">
-        <v>284</v>
+        <v>714</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>28</v>
@@ -17163,7 +17904,7 @@
         <v>63</v>
       </c>
       <c r="B28" t="s">
-        <v>285</v>
+        <v>715</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>28</v>
@@ -17230,7 +17971,7 @@
         <v>63</v>
       </c>
       <c r="B29" t="s">
-        <v>286</v>
+        <v>716</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>28</v>
@@ -17297,7 +18038,7 @@
         <v>63</v>
       </c>
       <c r="B30" t="s">
-        <v>287</v>
+        <v>717</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>28</v>
@@ -17364,7 +18105,7 @@
         <v>63</v>
       </c>
       <c r="B31" t="s">
-        <v>288</v>
+        <v>718</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>28</v>
@@ -17431,7 +18172,7 @@
         <v>63</v>
       </c>
       <c r="B32" t="s">
-        <v>289</v>
+        <v>719</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>28</v>
@@ -17498,7 +18239,7 @@
         <v>63</v>
       </c>
       <c r="B33" t="s">
-        <v>290</v>
+        <v>720</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>28</v>
@@ -17565,7 +18306,7 @@
         <v>63</v>
       </c>
       <c r="B34" t="s">
-        <v>291</v>
+        <v>721</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>28</v>
@@ -17632,7 +18373,7 @@
         <v>63</v>
       </c>
       <c r="B35" t="s">
-        <v>292</v>
+        <v>722</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>28</v>
@@ -17699,7 +18440,7 @@
         <v>63</v>
       </c>
       <c r="B36" t="s">
-        <v>293</v>
+        <v>884</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>28</v>
@@ -17766,7 +18507,7 @@
         <v>63</v>
       </c>
       <c r="B37" t="s">
-        <v>294</v>
+        <v>885</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>28</v>
@@ -17833,7 +18574,7 @@
         <v>63</v>
       </c>
       <c r="B38" t="s">
-        <v>295</v>
+        <v>725</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>28</v>
@@ -17900,7 +18641,7 @@
         <v>63</v>
       </c>
       <c r="B39" t="s">
-        <v>120</v>
+        <v>726</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>28</v>
@@ -17967,7 +18708,7 @@
         <v>63</v>
       </c>
       <c r="B40" t="s">
-        <v>121</v>
+        <v>727</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>28</v>
@@ -18034,7 +18775,7 @@
         <v>63</v>
       </c>
       <c r="B41" t="s">
-        <v>122</v>
+        <v>728</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>28</v>
@@ -18101,7 +18842,7 @@
         <v>63</v>
       </c>
       <c r="B42" t="s">
-        <v>123</v>
+        <v>729</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>28</v>
@@ -18168,7 +18909,7 @@
         <v>63</v>
       </c>
       <c r="B43" t="s">
-        <v>124</v>
+        <v>730</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>28</v>
@@ -18235,7 +18976,7 @@
         <v>63</v>
       </c>
       <c r="B44" t="s">
-        <v>125</v>
+        <v>731</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>28</v>
@@ -18302,7 +19043,7 @@
         <v>63</v>
       </c>
       <c r="B45" t="s">
-        <v>398</v>
+        <v>732</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>28</v>
@@ -18369,7 +19110,7 @@
         <v>63</v>
       </c>
       <c r="B46" t="s">
-        <v>126</v>
+        <v>733</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>28</v>
@@ -18436,7 +19177,7 @@
         <v>63</v>
       </c>
       <c r="B47" t="s">
-        <v>399</v>
+        <v>734</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>28</v>
@@ -18503,7 +19244,7 @@
         <v>63</v>
       </c>
       <c r="B48" t="s">
-        <v>127</v>
+        <v>735</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>28</v>
@@ -18570,7 +19311,7 @@
         <v>63</v>
       </c>
       <c r="B49" t="s">
-        <v>128</v>
+        <v>736</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>28</v>
@@ -18637,7 +19378,7 @@
         <v>63</v>
       </c>
       <c r="B50" t="s">
-        <v>129</v>
+        <v>737</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>28</v>
@@ -18820,7 +19561,7 @@
         <v>63</v>
       </c>
       <c r="B2" t="s">
-        <v>580</v>
+        <v>738</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>28</v>
@@ -18887,7 +19628,7 @@
         <v>63</v>
       </c>
       <c r="B3" t="s">
-        <v>581</v>
+        <v>739</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>28</v>
@@ -18954,7 +19695,7 @@
         <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>582</v>
+        <v>740</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>28</v>
@@ -19021,7 +19762,7 @@
         <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>583</v>
+        <v>741</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>28</v>
@@ -19088,7 +19829,7 @@
         <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>584</v>
+        <v>742</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>28</v>
@@ -19155,7 +19896,7 @@
         <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>585</v>
+        <v>743</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>28</v>
@@ -19222,7 +19963,7 @@
         <v>63</v>
       </c>
       <c r="B8" t="s">
-        <v>586</v>
+        <v>744</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>28</v>
@@ -19289,7 +20030,7 @@
         <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>587</v>
+        <v>745</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>28</v>
@@ -19356,7 +20097,7 @@
         <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>588</v>
+        <v>746</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>28</v>
@@ -19423,7 +20164,7 @@
         <v>63</v>
       </c>
       <c r="B11" t="s">
-        <v>589</v>
+        <v>747</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>28</v>
@@ -19490,7 +20231,7 @@
         <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>590</v>
+        <v>748</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>28</v>
@@ -19557,7 +20298,7 @@
         <v>63</v>
       </c>
       <c r="B13" t="s">
-        <v>591</v>
+        <v>749</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>28</v>
@@ -19624,7 +20365,7 @@
         <v>63</v>
       </c>
       <c r="B14" t="s">
-        <v>592</v>
+        <v>750</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>28</v>
@@ -19691,7 +20432,7 @@
         <v>63</v>
       </c>
       <c r="B15" t="s">
-        <v>593</v>
+        <v>751</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>28</v>
@@ -19758,7 +20499,7 @@
         <v>63</v>
       </c>
       <c r="B16" t="s">
-        <v>594</v>
+        <v>752</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>28</v>
@@ -19825,7 +20566,7 @@
         <v>63</v>
       </c>
       <c r="B17" t="s">
-        <v>595</v>
+        <v>753</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>28</v>
@@ -19892,7 +20633,7 @@
         <v>63</v>
       </c>
       <c r="B18" t="s">
-        <v>596</v>
+        <v>754</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>28</v>
@@ -19959,7 +20700,7 @@
         <v>63</v>
       </c>
       <c r="B19" t="s">
-        <v>597</v>
+        <v>755</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>28</v>
@@ -20026,7 +20767,7 @@
         <v>63</v>
       </c>
       <c r="B20" t="s">
-        <v>598</v>
+        <v>756</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>28</v>
@@ -20093,7 +20834,7 @@
         <v>63</v>
       </c>
       <c r="B21" t="s">
-        <v>599</v>
+        <v>757</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>28</v>
@@ -20160,7 +20901,7 @@
         <v>63</v>
       </c>
       <c r="B22" t="s">
-        <v>600</v>
+        <v>758</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>28</v>
@@ -20227,7 +20968,7 @@
         <v>63</v>
       </c>
       <c r="B23" t="s">
-        <v>601</v>
+        <v>759</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>28</v>
@@ -20294,7 +21035,7 @@
         <v>63</v>
       </c>
       <c r="B24" t="s">
-        <v>602</v>
+        <v>760</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>28</v>
@@ -20361,7 +21102,7 @@
         <v>63</v>
       </c>
       <c r="B25" t="s">
-        <v>603</v>
+        <v>761</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>28</v>
@@ -20428,7 +21169,7 @@
         <v>63</v>
       </c>
       <c r="B26" t="s">
-        <v>604</v>
+        <v>762</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>28</v>
@@ -20495,7 +21236,7 @@
         <v>63</v>
       </c>
       <c r="B27" t="s">
-        <v>605</v>
+        <v>763</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>28</v>
@@ -20562,7 +21303,7 @@
         <v>63</v>
       </c>
       <c r="B28" t="s">
-        <v>606</v>
+        <v>764</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>28</v>
@@ -20629,7 +21370,7 @@
         <v>63</v>
       </c>
       <c r="B29" t="s">
-        <v>607</v>
+        <v>765</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>28</v>
@@ -20696,7 +21437,7 @@
         <v>63</v>
       </c>
       <c r="B30" t="s">
-        <v>608</v>
+        <v>766</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>28</v>
@@ -20763,7 +21504,7 @@
         <v>63</v>
       </c>
       <c r="B31" t="s">
-        <v>609</v>
+        <v>767</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>28</v>
@@ -20830,7 +21571,7 @@
         <v>63</v>
       </c>
       <c r="B32" t="s">
-        <v>610</v>
+        <v>768</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>28</v>
@@ -20897,7 +21638,7 @@
         <v>63</v>
       </c>
       <c r="B33" t="s">
-        <v>611</v>
+        <v>769</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>28</v>
@@ -20964,7 +21705,7 @@
         <v>63</v>
       </c>
       <c r="B34" t="s">
-        <v>612</v>
+        <v>770</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>28</v>
@@ -21031,7 +21772,7 @@
         <v>63</v>
       </c>
       <c r="B35" t="s">
-        <v>613</v>
+        <v>771</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>28</v>
@@ -21098,7 +21839,7 @@
         <v>63</v>
       </c>
       <c r="B36" t="s">
-        <v>614</v>
+        <v>772</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>28</v>
@@ -21165,7 +21906,7 @@
         <v>63</v>
       </c>
       <c r="B37" t="s">
-        <v>615</v>
+        <v>773</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>28</v>
@@ -21232,7 +21973,7 @@
         <v>63</v>
       </c>
       <c r="B38" t="s">
-        <v>616</v>
+        <v>774</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>28</v>
@@ -21299,7 +22040,7 @@
         <v>63</v>
       </c>
       <c r="B39" t="s">
-        <v>617</v>
+        <v>775</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>28</v>
@@ -21366,7 +22107,7 @@
         <v>63</v>
       </c>
       <c r="B40" t="s">
-        <v>618</v>
+        <v>776</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>28</v>
@@ -21433,7 +22174,7 @@
         <v>63</v>
       </c>
       <c r="B41" t="s">
-        <v>619</v>
+        <v>777</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>28</v>
@@ -21500,7 +22241,7 @@
         <v>63</v>
       </c>
       <c r="B42" t="s">
-        <v>620</v>
+        <v>778</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>28</v>
@@ -21567,7 +22308,7 @@
         <v>63</v>
       </c>
       <c r="B43" t="s">
-        <v>621</v>
+        <v>779</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>28</v>
@@ -21634,7 +22375,7 @@
         <v>63</v>
       </c>
       <c r="B44" t="s">
-        <v>622</v>
+        <v>780</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>28</v>
@@ -21701,7 +22442,7 @@
         <v>63</v>
       </c>
       <c r="B45" t="s">
-        <v>623</v>
+        <v>781</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>28</v>
@@ -21768,7 +22509,7 @@
         <v>63</v>
       </c>
       <c r="B46" t="s">
-        <v>624</v>
+        <v>782</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>28</v>
@@ -21835,7 +22576,7 @@
         <v>63</v>
       </c>
       <c r="B47" t="s">
-        <v>625</v>
+        <v>783</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>28</v>
@@ -21902,7 +22643,7 @@
         <v>63</v>
       </c>
       <c r="B48" t="s">
-        <v>626</v>
+        <v>784</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>28</v>
@@ -21969,7 +22710,7 @@
         <v>63</v>
       </c>
       <c r="B49" t="s">
-        <v>627</v>
+        <v>785</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>28</v>
@@ -22036,7 +22777,7 @@
         <v>63</v>
       </c>
       <c r="B50" t="s">
-        <v>628</v>
+        <v>786</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>28</v>
@@ -22229,7 +22970,7 @@
         <v>63</v>
       </c>
       <c r="B2" t="s">
-        <v>509</v>
+        <v>787</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>47</v>
@@ -22296,7 +23037,7 @@
         <v>63</v>
       </c>
       <c r="B3" t="s">
-        <v>510</v>
+        <v>788</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>47</v>
@@ -22363,7 +23104,7 @@
         <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>511</v>
+        <v>789</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>47</v>
@@ -22430,7 +23171,7 @@
         <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>512</v>
+        <v>790</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>47</v>
@@ -22494,10 +23235,10 @@
     </row>
     <row ht="72.5" r="6" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>462</v>
+        <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>513</v>
+        <v>791</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>47</v>
@@ -22564,7 +23305,7 @@
         <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>514</v>
+        <v>792</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>47</v>
@@ -22631,7 +23372,7 @@
         <v>63</v>
       </c>
       <c r="B8" t="s">
-        <v>515</v>
+        <v>793</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>47</v>
@@ -22695,10 +23436,10 @@
     </row>
     <row ht="72.5" r="9" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>462</v>
+        <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>516</v>
+        <v>794</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>47</v>
@@ -22765,7 +23506,7 @@
         <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>517</v>
+        <v>795</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>47</v>
@@ -22951,7 +23692,7 @@
         <v>63</v>
       </c>
       <c r="B2" t="s">
-        <v>518</v>
+        <v>796</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>47</v>
@@ -23015,10 +23756,10 @@
     </row>
     <row ht="72.5" r="3" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>462</v>
+        <v>63</v>
       </c>
       <c r="B3" t="s">
-        <v>519</v>
+        <v>797</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>47</v>
@@ -23085,7 +23826,7 @@
         <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>520</v>
+        <v>798</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>47</v>
@@ -23149,10 +23890,10 @@
     </row>
     <row ht="72.5" r="5" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>462</v>
+        <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>521</v>
+        <v>799</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>47</v>
@@ -23216,10 +23957,10 @@
     </row>
     <row ht="72.5" r="6" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>462</v>
+        <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>522</v>
+        <v>800</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>47</v>
@@ -23283,10 +24024,10 @@
     </row>
     <row ht="72.5" r="7" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>462</v>
+        <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>523</v>
+        <v>801</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>47</v>
@@ -23350,10 +24091,10 @@
     </row>
     <row ht="72.5" r="8" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>462</v>
+        <v>63</v>
       </c>
       <c r="B8" t="s">
-        <v>524</v>
+        <v>802</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>47</v>
@@ -23420,7 +24161,7 @@
         <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>525</v>
+        <v>803</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>47</v>
@@ -23484,10 +24225,10 @@
     </row>
     <row ht="72.5" r="10" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>462</v>
+        <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>526</v>
+        <v>804</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>47</v>
@@ -23800,7 +24541,7 @@
         <v>63</v>
       </c>
       <c r="B2" t="s">
-        <v>529</v>
+        <v>805</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>47</v>
@@ -24649,7 +25390,7 @@
         <v>63</v>
       </c>
       <c r="B2" t="s">
-        <v>195</v>
+        <v>806</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>47</v>
@@ -24716,7 +25457,7 @@
         <v>63</v>
       </c>
       <c r="B3" t="s">
-        <v>196</v>
+        <v>807</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>47</v>
@@ -24783,7 +25524,7 @@
         <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>197</v>
+        <v>808</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>47</v>
@@ -24850,7 +25591,7 @@
         <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>198</v>
+        <v>809</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>47</v>
@@ -24917,7 +25658,7 @@
         <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>199</v>
+        <v>810</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>47</v>
@@ -24984,7 +25725,7 @@
         <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>200</v>
+        <v>811</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>47</v>
@@ -25051,7 +25792,7 @@
         <v>63</v>
       </c>
       <c r="B8" t="s">
-        <v>201</v>
+        <v>812</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>47</v>
@@ -25118,7 +25859,7 @@
         <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>202</v>
+        <v>813</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>47</v>
@@ -25185,7 +25926,7 @@
         <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>203</v>
+        <v>814</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>47</v>
@@ -25499,7 +26240,7 @@
         <v>63</v>
       </c>
       <c r="B2" t="s">
-        <v>473</v>
+        <v>815</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>42</v>
@@ -25564,10 +26305,10 @@
     </row>
     <row ht="58" r="3" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>462</v>
+        <v>63</v>
       </c>
       <c r="B3" t="s">
-        <v>474</v>
+        <v>816</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>42</v>
@@ -25635,7 +26376,7 @@
         <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>475</v>
+        <v>817</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>42</v>
@@ -25703,7 +26444,7 @@
         <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>476</v>
+        <v>818</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>42</v>
@@ -25771,7 +26512,7 @@
         <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>477</v>
+        <v>819</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>42</v>
@@ -25839,7 +26580,7 @@
         <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>478</v>
+        <v>820</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>42</v>
@@ -25904,10 +26645,10 @@
     </row>
     <row ht="58" r="8" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>462</v>
+        <v>63</v>
       </c>
       <c r="B8" t="s">
-        <v>479</v>
+        <v>821</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>42</v>
@@ -25975,7 +26716,7 @@
         <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>480</v>
+        <v>822</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>42</v>
@@ -26040,10 +26781,10 @@
     </row>
     <row ht="58" r="10" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>462</v>
+        <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>481</v>
+        <v>823</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>42</v>
